--- a/erp-server/erp-server-plm/src/main/resources/excel/skuStdCostDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/skuStdCostDetailTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23835" windowHeight="11700"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,6 +30,13 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -45,6 +52,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -59,34 +73,10 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>生效日期</t>
-    </r>
+    <t>生效日期</t>
   </si>
   <si>
-    <r>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>币别</t>
-    </r>
+    <t>币别</t>
   </si>
 </sst>
 </file>
@@ -709,7 +699,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -720,6 +710,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1049,10 +1045,10 @@
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
     </row>

--- a/erp-server/erp-server-plm/src/main/resources/excel/skuStdCostDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/skuStdCostDetailTemplate.xlsx
@@ -1053,6 +1053,11 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
+      <formula1>"CNY,RUB,USD,EUR,GBP,JPY,HKD,THB,CAD,SGD,NZD,KRW,INR,ZAR,PHP,AUD,MYR,TWD,AED,DKK,NOK,CHF,SAR,TRY,VND,CZK,PLN,MXN,IDR,BRL,SEK,MOP,BYN,HUF,ILS,KES"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
